--- a/salidas/empresas/PLTR.xlsx
+++ b/salidas/empresas/PLTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B4" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B5" t="n">
@@ -570,7 +582,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B6" t="n">
@@ -595,7 +607,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B7" t="n">
@@ -620,7 +632,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B8" t="n">
@@ -645,7 +657,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B9" t="n">
@@ -670,7 +682,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B10" t="n">
@@ -695,7 +707,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B11" t="n">
@@ -720,7 +732,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B12" t="n">
@@ -745,7 +757,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B13" t="n">
@@ -770,7 +782,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B14" t="n">
@@ -795,7 +807,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B15" t="n">
@@ -820,7 +832,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B16" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B17" t="n">
@@ -870,7 +882,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B18" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B19" t="n">
@@ -922,7 +934,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B20" t="n">
@@ -949,7 +961,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B21" t="n">
@@ -976,7 +988,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B22" t="n">
@@ -1003,7 +1015,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B23" t="n">
@@ -1030,7 +1042,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B24" t="n">
@@ -1057,7 +1069,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B25" t="n">
@@ -1084,7 +1096,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B26" t="n">
@@ -1111,7 +1123,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B27" t="n">
@@ -1138,7 +1150,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B28" t="n">
@@ -1165,7 +1177,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B29" t="n">
@@ -1192,7 +1204,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B30" t="n">
@@ -1219,7 +1231,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B31" t="n">
@@ -1246,7 +1258,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B32" t="n">
@@ -1273,7 +1285,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B33" t="n">
@@ -1300,7 +1312,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B34" t="n">
@@ -1327,7 +1339,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B35" t="n">
@@ -1354,7 +1366,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B36" t="n">
@@ -1381,7 +1393,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B37" t="n">
@@ -1408,7 +1420,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B38" t="n">
@@ -1435,7 +1447,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B39" t="n">
@@ -1462,7 +1474,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B40" t="n">
@@ -1491,7 +1503,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B41" t="n">
@@ -1520,7 +1532,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B42" t="n">
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B43" t="n">
@@ -1578,7 +1590,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B44" t="n">
@@ -1607,7 +1619,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B45" t="n">
@@ -1636,7 +1648,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B46" t="n">
@@ -1665,7 +1677,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B47" t="n">
@@ -1694,7 +1706,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B48" t="n">
@@ -1723,7 +1735,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B49" t="n">
@@ -1752,7 +1764,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B50" t="n">
@@ -1781,7 +1793,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B51" t="n">
@@ -1810,7 +1822,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B52" t="n">
@@ -1839,7 +1851,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B53" t="n">
@@ -1868,7 +1880,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B54" t="n">
@@ -1897,7 +1909,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B55" t="n">
@@ -1926,7 +1938,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B56" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B57" t="n">
@@ -1984,7 +1996,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B58" t="n">
@@ -2013,7 +2025,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B59" t="n">
@@ -2042,7 +2054,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B60" t="n">
@@ -2071,7 +2083,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B61" t="n">
@@ -2100,7 +2112,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B62" t="n">
@@ -2129,7 +2141,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B63" t="n">
@@ -2158,7 +2170,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B64" t="n">
@@ -2187,7 +2199,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B65" t="n">
@@ -2216,7 +2228,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B66" t="n">
@@ -2245,7 +2257,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B67" t="n">
@@ -2274,7 +2286,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B68" t="n">
@@ -2303,7 +2315,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B69" t="n">
@@ -2332,7 +2344,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B70" t="n">
@@ -2361,7 +2373,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B71" t="n">
@@ -2390,7 +2402,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B72" t="n">
@@ -2419,7 +2431,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B73" t="n">
@@ -2448,32 +2460,32 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B74" t="n">
-        <v>191.7899932861328</v>
+        <v>192.5899963378906</v>
       </c>
       <c r="C74" t="n">
-        <v>191.7899932861328</v>
+        <v>192.5899963378906</v>
       </c>
       <c r="D74" t="n">
-        <v>435670700</v>
+        <v>458400400</v>
       </c>
       <c r="E74" t="n">
         <v>1.17</v>
       </c>
       <c r="F74" t="n">
-        <v>163.9230711847289</v>
+        <v>164.6068344768296</v>
       </c>
       <c r="G74" t="n">
         <v>2402897000</v>
       </c>
       <c r="H74" t="n">
-        <v>460851599497.2687</v>
+        <v>462773924430.3284</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1813106013283133</v>
+        <v>0.190769891510123</v>
       </c>
     </row>
   </sheetData>
@@ -2505,75 +2517,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -2609,13 +2621,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>44328</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -2651,13 +2663,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -2693,13 +2705,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -2735,13 +2747,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>44328</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -2777,13 +2789,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -2819,13 +2831,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -2861,13 +2873,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -2894,7 +2906,7 @@
       <c r="I9" t="n">
         <v>-0.27</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K9" t="n">
@@ -2907,13 +2919,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -2940,7 +2952,7 @@
       <c r="I10" t="n">
         <v>-0.25</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="K10" t="n">
@@ -2953,13 +2965,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -2986,7 +2998,7 @@
       <c r="I11" t="n">
         <v>-0.27</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="K11" t="n">
@@ -2999,13 +3011,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>44872</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -3032,7 +3044,7 @@
       <c r="I12" t="n">
         <v>-0.28</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>44872</v>
       </c>
       <c r="K12" t="n">
@@ -3045,13 +3057,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -3078,7 +3090,7 @@
       <c r="I13" t="n">
         <v>-0.18</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K13" t="n">
@@ -3091,13 +3103,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -3124,7 +3136,7 @@
       <c r="I14" t="n">
         <v>-0.12</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="K14" t="n">
@@ -3137,13 +3149,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -3170,7 +3182,7 @@
       <c r="I15" t="n">
         <v>-0.01999999999999998</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="K15" t="n">
@@ -3183,13 +3195,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -3216,7 +3228,7 @@
       <c r="I16" t="n">
         <v>0.07000000000000002</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K16" t="n">
@@ -3229,13 +3241,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -3262,7 +3274,7 @@
       <c r="I17" t="n">
         <v>0.09</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K17" t="n">
@@ -3275,13 +3287,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3308,7 +3320,7 @@
       <c r="I18" t="n">
         <v>0.12</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="K18" t="n">
@@ -3321,13 +3333,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -3354,7 +3366,7 @@
       <c r="I19" t="n">
         <v>0.17</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="K19" t="n">
@@ -3367,13 +3379,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -3400,7 +3412,7 @@
       <c r="I20" t="n">
         <v>0.2</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="K20" t="n">
@@ -3413,13 +3425,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -3446,7 +3458,7 @@
       <c r="I21" t="n">
         <v>0.19</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="K21" t="n">
@@ -3459,13 +3471,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -3492,7 +3504,7 @@
       <c r="I22" t="n">
         <v>0.23</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K22" t="n">
@@ -3505,13 +3517,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -3538,7 +3550,7 @@
       <c r="I23" t="n">
         <v>0.3</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K23" t="n">
@@ -3551,13 +3563,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -3584,7 +3596,7 @@
       <c r="I24" t="n">
         <v>0.42</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K24" t="n">
@@ -3597,13 +3609,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -3630,7 +3642,7 @@
       <c r="I25" t="n">
         <v>0.63</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="K25" t="n">
@@ -3643,13 +3655,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -3676,7 +3688,7 @@
       <c r="I26" t="n">
         <v>0.89</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K26" t="n">
@@ -3689,13 +3701,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -3722,7 +3734,7 @@
       <c r="I27" t="n">
         <v>1.17</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K27" t="n">
@@ -3759,52 +3771,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="C2" t="n">
@@ -3833,10 +3845,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="C3" t="n">
@@ -3865,10 +3877,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C4" t="n">
@@ -3897,10 +3909,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44328</v>
       </c>
       <c r="C5" t="n">
@@ -3929,10 +3941,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="C6" t="n">
@@ -3961,10 +3973,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="C7" t="n">
@@ -3993,10 +4005,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C8" t="n">
@@ -4025,10 +4037,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="C9" t="n">
@@ -4057,10 +4069,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="C10" t="n">
@@ -4089,10 +4101,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44872</v>
       </c>
       <c r="C11" t="n">
@@ -4121,10 +4133,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C12" t="n">
@@ -4153,10 +4165,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="C13" t="n">
@@ -4185,10 +4197,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="C14" t="n">
@@ -4217,10 +4229,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C15" t="n">
@@ -4249,10 +4261,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C16" t="n">
@@ -4281,10 +4293,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C17" t="n">
@@ -4313,10 +4325,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="C18" t="n">
@@ -4345,10 +4357,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="C19" t="n">
@@ -4377,10 +4389,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C20" t="n">
@@ -4409,10 +4421,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C21" t="n">
@@ -4441,10 +4453,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C22" t="n">
@@ -4473,10 +4485,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C23" t="n">
@@ -4505,10 +4517,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="C24" t="n">
@@ -4537,10 +4549,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C25" t="n">
@@ -4569,10 +4581,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C26" t="n">
@@ -4619,12 +4631,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
